--- a/artfynd/A 14564-2025 artfynd.xlsx
+++ b/artfynd/A 14564-2025 artfynd.xlsx
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-01-28</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-01-28</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-01-28</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-01-28</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -994,12 +994,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-01-28</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-01-28</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-01-28</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-01-28</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-01-28</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-01-28</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 14564-2025 artfynd.xlsx
+++ b/artfynd/A 14564-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133426851</v>
       </c>
       <c r="B2" t="n">
-        <v>96241</v>
+        <v>96243</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>133426847</v>
       </c>
       <c r="B3" t="n">
-        <v>80398</v>
+        <v>80399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>133426848</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>133426854</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 14564-2025 artfynd.xlsx
+++ b/artfynd/A 14564-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133426851</v>
       </c>
       <c r="B2" t="n">
-        <v>96243</v>
+        <v>96251</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>133426848</v>
       </c>
       <c r="B5" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 14564-2025 artfynd.xlsx
+++ b/artfynd/A 14564-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133426851</v>
       </c>
       <c r="B2" t="n">
-        <v>96251</v>
+        <v>96279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>133426847</v>
       </c>
       <c r="B3" t="n">
-        <v>80399</v>
+        <v>80413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>133426850</v>
       </c>
       <c r="B4" t="n">
-        <v>75433</v>
+        <v>75444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>133426848</v>
       </c>
       <c r="B5" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>133426854</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 14564-2025 artfynd.xlsx
+++ b/artfynd/A 14564-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133426851</v>
       </c>
       <c r="B2" t="n">
-        <v>96279</v>
+        <v>96289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>133426847</v>
       </c>
       <c r="B3" t="n">
-        <v>80413</v>
+        <v>80423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>133426850</v>
       </c>
       <c r="B4" t="n">
-        <v>75444</v>
+        <v>75454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>133426848</v>
       </c>
       <c r="B5" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>133426854</v>
       </c>
       <c r="B6" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 14564-2025 artfynd.xlsx
+++ b/artfynd/A 14564-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133426851</v>
       </c>
       <c r="B2" t="n">
-        <v>96289</v>
+        <v>96291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>133426847</v>
       </c>
       <c r="B3" t="n">
-        <v>80423</v>
+        <v>80424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>133426848</v>
       </c>
       <c r="B5" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>133426854</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 14564-2025 artfynd.xlsx
+++ b/artfynd/A 14564-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133426851</v>
       </c>
       <c r="B2" t="n">
-        <v>96292</v>
+        <v>96306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,42 +795,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133426847</v>
+        <v>133426854</v>
       </c>
       <c r="B3" t="n">
-        <v>80424</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -923,11 +923,11 @@
         <v>133426850</v>
       </c>
       <c r="B4" t="n">
-        <v>75454</v>
+        <v>75468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1048,7 +1048,7 @@
         <v>133426848</v>
       </c>
       <c r="B5" t="n">
-        <v>99181</v>
+        <v>99195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,42 +1155,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133426854</v>
+        <v>133426847</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>80438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1248,17 +1248,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 14564-2025 artfynd.xlsx
+++ b/artfynd/A 14564-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Forkningsprojekt effekter av torka i nyckelbiotoper</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133426851</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,6 +927,11 @@
           <t>Forkningsprojekt effekter av torka i nyckelbiotoper</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133426854</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1042,6 +1057,11 @@
           <t>Forkningsprojekt effekter av torka i nyckelbiotoper</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133426850</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
           <t>Forkningsprojekt effekter av torka i nyckelbiotoper</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133426848</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,8 +1302,20 @@
           <t>Forkningsprojekt effekter av torka i nyckelbiotoper</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133426847</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>